--- a/output/pdf_financials_xlsx/FEC.xlsx
+++ b/output/pdf_financials_xlsx/FEC.xlsx
@@ -4409,7 +4409,7 @@
         <v>115.922</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>0</v>
+        <v>52.152</v>
       </c>
       <c r="P69" s="3" t="n">
         <v>9.509</v>
@@ -4519,7 +4519,7 @@
         <v>115.922</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>52.152</v>
       </c>
       <c r="P71" s="3" t="n">
         <v>9.509</v>
@@ -4739,7 +4739,7 @@
         <v>36.555</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>119.343</v>
+        <v>67.191</v>
       </c>
       <c r="P75" s="3" t="n">
         <v>107.051</v>
@@ -4849,10 +4849,10 @@
         <v>392.535</v>
       </c>
       <c r="O77" s="3" t="n">
-        <v>123.944</v>
+        <v>71.792</v>
       </c>
       <c r="P77" s="3" t="n">
-        <v>103.961</v>
+        <v>73.452</v>
       </c>
       <c r="Q77" s="3" t="n">
         <v>0</v>
@@ -4959,10 +4959,10 @@
         <v>392.535</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>123.944</v>
+        <v>71.792</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>103.961</v>
+        <v>73.452</v>
       </c>
       <c r="Q79" s="3" t="n">
         <v>0</v>
@@ -5021,7 +5021,7 @@
         <v>0.06758150112895742</v>
       </c>
       <c r="P80" s="3" t="n">
-        <v>0.06573653362747831</v>
+        <v>0.04806176580831257</v>
       </c>
       <c r="Q80" s="1" t="inlineStr">
         <is>
@@ -5295,10 +5295,10 @@
         <v>133.049</v>
       </c>
       <c r="O85" s="3" t="n">
-        <v>499.322</v>
+        <v>551.474</v>
       </c>
       <c r="P85" s="3" t="n">
-        <v>528.3200000000001</v>
+        <v>558.829</v>
       </c>
       <c r="Q85" s="3" t="n">
         <v>687.759</v>
@@ -7420,25 +7420,25 @@
         <v>0</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-7.615</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-33.319</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>-40</v>
+        <v>-51.681</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>-45.14</v>
+        <v>-50.408</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>-42.728</v>
+        <v>-47.263</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>-57.5</v>
+        <v>-6.947</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-7.444</v>
       </c>
     </row>
     <row r="125">
@@ -7475,25 +7475,25 @@
         <v>0</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-7.615</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-33.319</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>-40</v>
+        <v>-51.681</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>-45.14</v>
+        <v>-50.408</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>-42.728</v>
+        <v>-47.263</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>-57.5</v>
+        <v>-6.947</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-7.444</v>
       </c>
     </row>
     <row r="126">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LongTermDebt</t>
+          <t>CurrentDebt</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -16350,7 +16350,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LongTermDebt</t>
+          <t>CurrentDebt</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -45696,7 +45696,11 @@
           <t>Lease payments 21</t>
         </is>
       </c>
-      <c r="D399" t="inlineStr"/>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E399" t="inlineStr">
         <is>
           <t>-</t>
@@ -49168,7 +49172,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D437" t="inlineStr"/>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E437" t="inlineStr">
         <is>
           <t>-</t>
@@ -51250,7 +51258,11 @@
           <t>Lease payments 18</t>
         </is>
       </c>
-      <c r="D459" t="inlineStr"/>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E459" t="inlineStr">
         <is>
           <t>-</t>
@@ -53412,7 +53424,11 @@
           <t>Lease payments 19</t>
         </is>
       </c>
-      <c r="D482" t="inlineStr"/>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E482" t="inlineStr">
         <is>
           <t>-</t>
@@ -55580,7 +55596,11 @@
           <t>Lease payments $</t>
         </is>
       </c>
-      <c r="D505" t="inlineStr"/>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E505" t="inlineStr">
         <is>
           <t>-</t>
@@ -91412,7 +91432,7 @@
       </c>
       <c r="D887" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E887" s="5" t="n">

--- a/output/pdf_financials_xlsx/FEC.xlsx
+++ b/output/pdf_financials_xlsx/FEC.xlsx
@@ -7521,25 +7521,25 @@
         <v>-207.553</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>0</v>
+        <v>-26.588</v>
       </c>
       <c r="I126" s="3" t="n">
-        <v>0</v>
+        <v>-41.846</v>
       </c>
       <c r="J126" s="3" t="n">
-        <v>0</v>
+        <v>-21.667</v>
       </c>
       <c r="K126" s="3" t="n">
-        <v>0</v>
+        <v>-25.485</v>
       </c>
       <c r="L126" s="3" t="n">
-        <v>0</v>
+        <v>-56.262</v>
       </c>
       <c r="M126" s="3" t="n">
-        <v>0</v>
+        <v>-15.721</v>
       </c>
       <c r="N126" s="3" t="n">
-        <v>0</v>
+        <v>-8.252000000000001</v>
       </c>
       <c r="O126" s="3" t="n">
         <v>0</v>
@@ -51356,7 +51356,11 @@
           <t>Dividends paid to non-controlling interests 20</t>
         </is>
       </c>
-      <c r="D460" t="inlineStr"/>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E460" t="inlineStr">
         <is>
           <t>-</t>
@@ -54094,7 +54098,11 @@
           <t>Dividends paid to non-controlling interests 21</t>
         </is>
       </c>
-      <c r="D489" t="inlineStr"/>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E489" t="inlineStr">
         <is>
           <t>-</t>
@@ -55030,7 +55038,11 @@
           <t>Additions to intangible assets 17</t>
         </is>
       </c>
-      <c r="D499" t="inlineStr"/>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E499" t="inlineStr">
         <is>
           <t>-</t>
@@ -55694,7 +55706,11 @@
           <t>Dividends paid to non-controlling interests 23</t>
         </is>
       </c>
-      <c r="D506" t="inlineStr"/>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E506" t="inlineStr">
         <is>
           <t>-</t>
@@ -61104,7 +61120,11 @@
           <t>Dividends paid to non-controlling interests 19</t>
         </is>
       </c>
-      <c r="D563" t="inlineStr"/>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E563" t="inlineStr">
         <is>
           <t>-</t>
@@ -63652,7 +63672,11 @@
           <t>Dividends paid to non-controlling interest 19</t>
         </is>
       </c>
-      <c r="D590" t="inlineStr"/>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E590" t="inlineStr">
         <is>
           <t>-</t>
@@ -65350,7 +65374,11 @@
           <t>Dividends paid to non-controlling interest</t>
         </is>
       </c>
-      <c r="D608" t="inlineStr"/>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E608" t="inlineStr">
         <is>
           <t>-</t>
@@ -66390,7 +66418,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D619" t="inlineStr"/>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E619" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/FEC.xlsx
+++ b/output/pdf_financials_xlsx/FEC.xlsx
@@ -957,18 +957,14 @@
       <c r="C11" s="3" t="n">
         <v>51.028</v>
       </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D11" s="3" t="n">
+        <v>1241.331</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>1031.989</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>4626.859</v>
+        <v>1148.148</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>-793.093</v>
@@ -1256,7 +1252,7 @@
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-1334.835</v>
+        <v>-1523.571</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>-5949.485</v>
@@ -1311,7 +1307,7 @@
         <v>-0</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0</v>
+        <v>188.736</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>50.226</v>
@@ -1323,10 +1319,10 @@
         <v>15.265</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>30.507</v>
+        <v>18.721</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>42.645</v>
+        <v>-147.727</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>1.039</v>
@@ -2043,7 +2039,7 @@
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1334.835</v>
+        <v>-1523.571</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-5949.485</v>
@@ -2163,7 +2159,7 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>306.742</v>
+        <v>118.006</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-4420.469</v>
@@ -2228,7 +2224,7 @@
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>6.196780539561239</v>
+        <v>2.383949000630704</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>-156.5019298676672</v>
@@ -2293,7 +2289,7 @@
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-0</v>
+        <v>-12.38773906828103</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>-0.8442075238445009</v>
@@ -2305,10 +2301,10 @@
         <v>-7.43980894824057</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-12.70913181136477</v>
+        <v>-7.799116813864355</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>26.97821246014475</v>
+        <v>93.45551394301332</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>0.1636150903819838</v>
@@ -6635,19 +6631,19 @@
         <v>0</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>10.902</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>30.34</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>160.747</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>59.529</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>6.966</v>
       </c>
       <c r="K110" s="3" t="n">
         <v>0</v>
@@ -7240,10 +7236,10 @@
         <v>0</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>0</v>
+        <v>-35.283</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>0</v>
+        <v>-165.978</v>
       </c>
       <c r="H121" s="3" t="n">
         <v>0</v>
@@ -7255,10 +7251,10 @@
         <v>0</v>
       </c>
       <c r="K121" s="3" t="n">
-        <v>0</v>
+        <v>-17.842</v>
       </c>
       <c r="L121" s="3" t="n">
-        <v>0</v>
+        <v>-21.752</v>
       </c>
       <c r="M121" s="3" t="n">
         <v>0</v>
@@ -47492,7 +47488,11 @@
           <t>Deferred income tax expense (recovery) 10</t>
         </is>
       </c>
-      <c r="D419" t="inlineStr"/>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E419" t="inlineStr">
         <is>
           <t>-</t>
@@ -51926,7 +51926,11 @@
           <t>Deferred income tax expense (recovery) 11</t>
         </is>
       </c>
-      <c r="D466" t="inlineStr"/>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E466" t="inlineStr">
         <is>
           <t>-</t>
@@ -54568,7 +54572,11 @@
           <t>Deferred income tax recovery 11</t>
         </is>
       </c>
-      <c r="D494" t="inlineStr"/>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E494" t="inlineStr">
         <is>
           <t>-</t>
@@ -55804,7 +55812,11 @@
           <t>Repurchase of common shares 24</t>
         </is>
       </c>
-      <c r="D507" t="inlineStr"/>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E507" t="inlineStr">
         <is>
           <t>-</t>
@@ -57122,7 +57134,11 @@
           <t>Deferred income tax recovery 10</t>
         </is>
       </c>
-      <c r="D521" t="inlineStr"/>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E521" t="inlineStr">
         <is>
           <t>-</t>
@@ -58750,7 +58766,11 @@
           <t>Repurchase of common shares 22</t>
         </is>
       </c>
-      <c r="D538" t="inlineStr"/>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E538" t="inlineStr">
         <is>
           <t>-</t>
@@ -59328,7 +59348,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D544" t="inlineStr"/>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E544" t="inlineStr">
         <is>
           <t>-</t>
@@ -59510,7 +59534,11 @@
           <t>Deferred income tax recovery 7</t>
         </is>
       </c>
-      <c r="D546" t="inlineStr"/>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E546" t="inlineStr">
         <is>
           <t>-</t>
@@ -62070,7 +62098,11 @@
           <t>Deferred income tax recovery 9</t>
         </is>
       </c>
-      <c r="D573" t="inlineStr"/>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E573" t="inlineStr">
         <is>
           <t>-</t>
@@ -65280,7 +65312,11 @@
           <t>Repurchase of common shares</t>
         </is>
       </c>
-      <c r="D607" t="inlineStr"/>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E607" t="inlineStr">
         <is>
           <t>-</t>
@@ -65942,7 +65978,11 @@
           <t>Deferred income tax expense 9</t>
         </is>
       </c>
-      <c r="D614" t="inlineStr"/>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E614" t="inlineStr">
         <is>
           <t>-</t>
@@ -69940,7 +69980,11 @@
           <t>Future income tax (note 15)</t>
         </is>
       </c>
-      <c r="D656" t="inlineStr"/>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E656" s="5" t="n">
         <v>57.04</v>
       </c>
@@ -74236,7 +74280,11 @@
           <t>Deferred income tax recovery (expense) 13</t>
         </is>
       </c>
-      <c r="D701" t="inlineStr"/>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E701" t="inlineStr">
         <is>
           <t>-</t>
@@ -76842,7 +76890,11 @@
           <t>Deferred income tax recovery (expense) 10</t>
         </is>
       </c>
-      <c r="D730" t="inlineStr"/>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E730" t="inlineStr">
         <is>
           <t>-</t>
@@ -81036,7 +81088,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D776" t="inlineStr"/>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E776" t="inlineStr">
         <is>
           <t>-</t>
@@ -81126,7 +81182,11 @@
           <t>Income tax recovery (expense) 11</t>
         </is>
       </c>
-      <c r="D777" t="inlineStr"/>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E777" t="inlineStr">
         <is>
           <t>-</t>
@@ -82766,7 +82826,11 @@
           <t>Deferred income tax recovery 10</t>
         </is>
       </c>
-      <c r="D795" t="inlineStr"/>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E795" t="inlineStr">
         <is>
           <t>-</t>
@@ -85208,7 +85272,11 @@
           <t>Deferred income tax recovery 9</t>
         </is>
       </c>
-      <c r="D821" t="inlineStr"/>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E821" t="inlineStr">
         <is>
           <t>-</t>
@@ -87004,7 +87072,11 @@
           <t>Total income tax recovery (expense)</t>
         </is>
       </c>
-      <c r="D840" t="inlineStr"/>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E840" t="inlineStr">
         <is>
           <t>-</t>
@@ -87666,7 +87738,11 @@
           <t>(Loss) earnings from operations</t>
         </is>
       </c>
-      <c r="D847" t="inlineStr"/>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E847" t="inlineStr">
         <is>
           <t>-</t>
@@ -89640,7 +89716,11 @@
           <t>Earnings from operations</t>
         </is>
       </c>
-      <c r="D868" t="inlineStr"/>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E868" t="inlineStr">
         <is>
           <t>-</t>
